--- a/outputs/Block5B_Senate_Cycle_Validation.xlsx
+++ b/outputs/Block5B_Senate_Cycle_Validation.xlsx
@@ -414,10 +414,10 @@
         <v>5.579313654851505</v>
       </c>
       <c r="C2">
-        <v>3.685780746769227</v>
+        <v>4.242390115056693</v>
       </c>
       <c r="D2">
-        <v>3.685780746769227</v>
+        <v>5.17823659291306</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -431,7 +431,7 @@
         <v>10.74361857330704</v>
       </c>
       <c r="C3">
-        <v>10.52453240292342</v>
+        <v>10.51886604841697</v>
       </c>
       <c r="D3">
         <v>10.74361857330704</v>
@@ -448,13 +448,13 @@
         <v>3.630910661152456</v>
       </c>
       <c r="C4">
-        <v>3.523966190174346</v>
+        <v>3.485106815936307</v>
       </c>
       <c r="D4">
-        <v>3.630910661152456</v>
+        <v>3.381502863335457</v>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -465,10 +465,10 @@
         <v>3.659578902902788</v>
       </c>
       <c r="C5">
-        <v>4.393383755473207</v>
+        <v>4.543570202377789</v>
       </c>
       <c r="D5">
-        <v>4.098446160475629</v>
+        <v>3.878601788930343</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -482,10 +482,10 @@
         <v>5.565711268516627</v>
       </c>
       <c r="C6">
-        <v>4.028977292767414</v>
+        <v>5.122173389106289</v>
       </c>
       <c r="D6">
-        <v>4.413160786704718</v>
+        <v>5.122173389106289</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
